--- a/research/traditional_assets/database/data/netherlands/netherlands_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.103</v>
+        <v>0.0122</v>
       </c>
       <c r="E2">
-        <v>0.07769999999999999</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F2">
-        <v>0.046</v>
+        <v>0.0462</v>
       </c>
       <c r="G2">
-        <v>0.1288099512001515</v>
+        <v>0.2316544796009021</v>
       </c>
       <c r="H2">
-        <v>0.1288099512001515</v>
+        <v>0.2316544796009021</v>
       </c>
       <c r="I2">
-        <v>0.1397515808083997</v>
+        <v>0.215212191621677</v>
       </c>
       <c r="J2">
-        <v>0.1104350794507737</v>
+        <v>0.1682285179808964</v>
       </c>
       <c r="K2">
-        <v>1041</v>
+        <v>972.2</v>
       </c>
       <c r="L2">
-        <v>0.09390137198834576</v>
+        <v>0.1328777420897971</v>
       </c>
       <c r="M2">
-        <v>654.5</v>
+        <v>413.9</v>
       </c>
       <c r="N2">
-        <v>0.1070091395124503</v>
+        <v>0.05988049941407097</v>
       </c>
       <c r="O2">
-        <v>0.6287223823246878</v>
+        <v>0.4257354453816087</v>
       </c>
       <c r="P2">
-        <v>528.8</v>
+        <v>339.7</v>
       </c>
       <c r="Q2">
-        <v>0.08645749881464283</v>
+        <v>0.04914570101705704</v>
       </c>
       <c r="R2">
-        <v>0.5079731027857829</v>
+        <v>0.3494137008845916</v>
       </c>
       <c r="S2">
-        <v>125.7</v>
+        <v>74.19999999999999</v>
       </c>
       <c r="T2">
-        <v>0.1920550038197098</v>
+        <v>0.1792703551582508</v>
       </c>
       <c r="U2">
-        <v>3074.5</v>
+        <v>2521.4</v>
       </c>
       <c r="V2">
-        <v>0.5026731847685693</v>
+        <v>0.3647806021324923</v>
       </c>
       <c r="W2">
-        <v>0.146667230229511</v>
+        <v>0.1188159953070004</v>
       </c>
       <c r="X2">
-        <v>0.07593755353513616</v>
+        <v>0.1032344544960029</v>
       </c>
       <c r="Y2">
-        <v>0.07072967669437481</v>
+        <v>0.01558154081099755</v>
       </c>
       <c r="Z2">
-        <v>0.7098329480916128</v>
+        <v>0.5141855186130028</v>
       </c>
       <c r="AA2">
-        <v>0.07839045801927416</v>
+        <v>0.08650066776350411</v>
       </c>
       <c r="AB2">
-        <v>0.04096213883625326</v>
+        <v>0.06830927534954948</v>
       </c>
       <c r="AC2">
-        <v>0.0374283191830209</v>
+        <v>0.01819139241395464</v>
       </c>
       <c r="AD2">
-        <v>9121.4</v>
+        <v>7268.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>9121.4</v>
+        <v>7268.5</v>
       </c>
       <c r="AG2">
-        <v>6046.9</v>
+        <v>4747.1</v>
       </c>
       <c r="AH2">
-        <v>0.5986074013794732</v>
+        <v>0.5125664640424241</v>
       </c>
       <c r="AI2">
-        <v>0.5272424596247441</v>
+        <v>0.5107619442472963</v>
       </c>
       <c r="AJ2">
-        <v>0.4971471323335964</v>
+        <v>0.4071548648277755</v>
       </c>
       <c r="AK2">
-        <v>0.4250687136661113</v>
+        <v>0.405412791541766</v>
       </c>
       <c r="AL2">
-        <v>366.4</v>
+        <v>355.4</v>
       </c>
       <c r="AM2">
-        <v>366.4</v>
+        <v>355.4</v>
       </c>
       <c r="AN2">
-        <v>5.798728544183089</v>
+        <v>4.514035523537449</v>
       </c>
       <c r="AO2">
-        <v>4.228438864628821</v>
+        <v>4.430500844119302</v>
       </c>
       <c r="AP2">
-        <v>3.844183089637635</v>
+        <v>2.948143087815178</v>
       </c>
       <c r="AQ2">
-        <v>4.228438864628821</v>
+        <v>4.430500844119302</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.103</v>
+        <v>0.0122</v>
       </c>
       <c r="E3">
-        <v>0.07769999999999999</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="F3">
-        <v>0.046</v>
+        <v>0.0462</v>
       </c>
       <c r="G3">
-        <v>0.1288099512001515</v>
+        <v>0.2316544796009021</v>
       </c>
       <c r="H3">
-        <v>0.1288099512001515</v>
+        <v>0.2316544796009021</v>
       </c>
       <c r="I3">
-        <v>0.1397515808083997</v>
+        <v>0.215212191621677</v>
       </c>
       <c r="J3">
-        <v>0.1104350794507737</v>
+        <v>0.1682285179808964</v>
       </c>
       <c r="K3">
-        <v>1041</v>
+        <v>972.2</v>
       </c>
       <c r="L3">
-        <v>0.09390137198834576</v>
+        <v>0.1328777420897971</v>
       </c>
       <c r="M3">
-        <v>654.5</v>
+        <v>413.9</v>
       </c>
       <c r="N3">
-        <v>0.1070091395124503</v>
+        <v>0.05988049941407097</v>
       </c>
       <c r="O3">
-        <v>0.6287223823246878</v>
+        <v>0.4257354453816087</v>
       </c>
       <c r="P3">
-        <v>528.8</v>
+        <v>339.7</v>
       </c>
       <c r="Q3">
-        <v>0.08645749881464283</v>
+        <v>0.04914570101705704</v>
       </c>
       <c r="R3">
-        <v>0.5079731027857829</v>
+        <v>0.3494137008845916</v>
       </c>
       <c r="S3">
-        <v>125.7</v>
+        <v>74.19999999999999</v>
       </c>
       <c r="T3">
-        <v>0.1920550038197098</v>
+        <v>0.1792703551582508</v>
       </c>
       <c r="U3">
-        <v>3074.5</v>
+        <v>2521.4</v>
       </c>
       <c r="V3">
-        <v>0.5026731847685693</v>
+        <v>0.3647806021324923</v>
       </c>
       <c r="W3">
-        <v>0.146667230229511</v>
+        <v>0.1188159953070004</v>
       </c>
       <c r="X3">
-        <v>0.07593755353513616</v>
+        <v>0.1032344544960029</v>
       </c>
       <c r="Y3">
-        <v>0.07072967669437481</v>
+        <v>0.01558154081099755</v>
       </c>
       <c r="Z3">
-        <v>0.7098329480916128</v>
+        <v>0.5141855186130028</v>
       </c>
       <c r="AA3">
-        <v>0.07839045801927416</v>
+        <v>0.08650066776350411</v>
       </c>
       <c r="AB3">
-        <v>0.04096213883625326</v>
+        <v>0.06830927534954948</v>
       </c>
       <c r="AC3">
-        <v>0.0374283191830209</v>
+        <v>0.01819139241395464</v>
       </c>
       <c r="AD3">
-        <v>9121.4</v>
+        <v>7268.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>9121.4</v>
+        <v>7268.5</v>
       </c>
       <c r="AG3">
-        <v>6046.9</v>
+        <v>4747.1</v>
       </c>
       <c r="AH3">
-        <v>0.5986074013794732</v>
+        <v>0.5125664640424241</v>
       </c>
       <c r="AI3">
-        <v>0.5272424596247441</v>
+        <v>0.5107619442472963</v>
       </c>
       <c r="AJ3">
-        <v>0.4971471323335964</v>
+        <v>0.4071548648277755</v>
       </c>
       <c r="AK3">
-        <v>0.4250687136661113</v>
+        <v>0.405412791541766</v>
       </c>
       <c r="AL3">
-        <v>366.4</v>
+        <v>355.4</v>
       </c>
       <c r="AM3">
-        <v>366.4</v>
+        <v>355.4</v>
       </c>
       <c r="AN3">
-        <v>5.798728544183089</v>
+        <v>4.514035523537449</v>
       </c>
       <c r="AO3">
-        <v>4.228438864628821</v>
+        <v>4.430500844119302</v>
       </c>
       <c r="AP3">
-        <v>3.844183089637635</v>
+        <v>2.948143087815178</v>
       </c>
       <c r="AQ3">
-        <v>4.228438864628821</v>
+        <v>4.430500844119302</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/netherlands/netherlands_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_insurance_general.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0122</v>
+        <v>0.106</v>
       </c>
       <c r="E2">
-        <v>0.06619999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="F2">
-        <v>0.0462</v>
+        <v>0.0731</v>
       </c>
       <c r="G2">
-        <v>0.2316544796009021</v>
+        <v>0.1217208443411647</v>
       </c>
       <c r="H2">
-        <v>0.2316544796009021</v>
+        <v>0.1217208443411647</v>
       </c>
       <c r="I2">
-        <v>0.215212191621677</v>
+        <v>0.5442271839684741</v>
       </c>
       <c r="J2">
-        <v>0.1682285179808964</v>
+        <v>0.4087661086764493</v>
       </c>
       <c r="K2">
-        <v>972.2</v>
+        <v>2828.6</v>
       </c>
       <c r="L2">
-        <v>0.1328777420897971</v>
+        <v>0.2499271053305883</v>
       </c>
       <c r="M2">
-        <v>413.9</v>
+        <v>427.96</v>
       </c>
       <c r="N2">
-        <v>0.05988049941407097</v>
+        <v>0.04332894603624582</v>
       </c>
       <c r="O2">
-        <v>0.4257354453816087</v>
+        <v>0.1512974616418016</v>
       </c>
       <c r="P2">
-        <v>339.7</v>
+        <v>422.5</v>
       </c>
       <c r="Q2">
-        <v>0.04914570101705704</v>
+        <v>0.0427761466032196</v>
       </c>
       <c r="R2">
-        <v>0.3494137008845916</v>
+        <v>0.149367178109312</v>
       </c>
       <c r="S2">
-        <v>74.19999999999999</v>
+        <v>5.45999999999998</v>
       </c>
       <c r="T2">
-        <v>0.1792703551582508</v>
+        <v>0.01275820170109351</v>
       </c>
       <c r="U2">
-        <v>2521.4</v>
+        <v>3640.8</v>
       </c>
       <c r="V2">
-        <v>0.3647806021324923</v>
+        <v>0.3686139516047383</v>
       </c>
       <c r="W2">
-        <v>0.1188159953070004</v>
+        <v>0.4078143021914648</v>
       </c>
       <c r="X2">
-        <v>0.1032344544960029</v>
+        <v>0.0895435617598952</v>
       </c>
       <c r="Y2">
-        <v>0.01558154081099755</v>
+        <v>0.3182707404315696</v>
       </c>
       <c r="Z2">
-        <v>0.5141855186130028</v>
+        <v>0.9056043657080673</v>
       </c>
       <c r="AA2">
-        <v>0.08650066776350411</v>
+        <v>0.3701803725708908</v>
       </c>
       <c r="AB2">
-        <v>0.06830927534954948</v>
+        <v>0.0609238952406246</v>
       </c>
       <c r="AC2">
-        <v>0.01819139241395464</v>
+        <v>0.3092564773302662</v>
       </c>
       <c r="AD2">
-        <v>7268.5</v>
+        <v>10278.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>7268.5</v>
+        <v>10278.4</v>
       </c>
       <c r="AG2">
-        <v>4747.1</v>
+        <v>6637.599999999999</v>
       </c>
       <c r="AH2">
-        <v>0.5125664640424241</v>
+        <v>0.5099576292209531</v>
       </c>
       <c r="AI2">
-        <v>0.5107619442472963</v>
+        <v>0.5991105204562809</v>
       </c>
       <c r="AJ2">
-        <v>0.4071548648277755</v>
+        <v>0.401923146791324</v>
       </c>
       <c r="AK2">
-        <v>0.405412791541766</v>
+        <v>0.4911174742699015</v>
       </c>
       <c r="AL2">
-        <v>355.4</v>
+        <v>1643</v>
       </c>
       <c r="AM2">
-        <v>355.4</v>
+        <v>1643</v>
       </c>
       <c r="AN2">
-        <v>4.514035523537449</v>
+        <v>1.655830138222122</v>
       </c>
       <c r="AO2">
-        <v>4.430500844119302</v>
+        <v>3.748874010955569</v>
       </c>
       <c r="AP2">
-        <v>2.948143087815178</v>
+        <v>1.069304378644843</v>
       </c>
       <c r="AQ2">
-        <v>4.430500844119302</v>
+        <v>3.748874010955569</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0122</v>
+        <v>0.106</v>
       </c>
       <c r="E3">
-        <v>0.06619999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="F3">
-        <v>0.0462</v>
+        <v>0.0731</v>
       </c>
       <c r="G3">
-        <v>0.2316544796009021</v>
+        <v>0.1217208443411647</v>
       </c>
       <c r="H3">
-        <v>0.2316544796009021</v>
+        <v>0.1217208443411647</v>
       </c>
       <c r="I3">
-        <v>0.215212191621677</v>
+        <v>0.5442271839684741</v>
       </c>
       <c r="J3">
-        <v>0.1682285179808964</v>
+        <v>0.4087661086764493</v>
       </c>
       <c r="K3">
-        <v>972.2</v>
+        <v>2828.6</v>
       </c>
       <c r="L3">
-        <v>0.1328777420897971</v>
+        <v>0.2499271053305883</v>
       </c>
       <c r="M3">
-        <v>413.9</v>
+        <v>427.96</v>
       </c>
       <c r="N3">
-        <v>0.05988049941407097</v>
+        <v>0.04332894603624582</v>
       </c>
       <c r="O3">
-        <v>0.4257354453816087</v>
+        <v>0.1512974616418016</v>
       </c>
       <c r="P3">
-        <v>339.7</v>
+        <v>422.5</v>
       </c>
       <c r="Q3">
-        <v>0.04914570101705704</v>
+        <v>0.0427761466032196</v>
       </c>
       <c r="R3">
-        <v>0.3494137008845916</v>
+        <v>0.149367178109312</v>
       </c>
       <c r="S3">
-        <v>74.19999999999999</v>
+        <v>5.45999999999998</v>
       </c>
       <c r="T3">
-        <v>0.1792703551582508</v>
+        <v>0.01275820170109351</v>
       </c>
       <c r="U3">
-        <v>2521.4</v>
+        <v>3640.8</v>
       </c>
       <c r="V3">
-        <v>0.3647806021324923</v>
+        <v>0.3686139516047383</v>
       </c>
       <c r="W3">
-        <v>0.1188159953070004</v>
+        <v>0.4078143021914648</v>
       </c>
       <c r="X3">
-        <v>0.1032344544960029</v>
+        <v>0.0895435617598952</v>
       </c>
       <c r="Y3">
-        <v>0.01558154081099755</v>
+        <v>0.3182707404315696</v>
       </c>
       <c r="Z3">
-        <v>0.5141855186130028</v>
+        <v>0.9056043657080673</v>
       </c>
       <c r="AA3">
-        <v>0.08650066776350411</v>
+        <v>0.3701803725708908</v>
       </c>
       <c r="AB3">
-        <v>0.06830927534954948</v>
+        <v>0.0609238952406246</v>
       </c>
       <c r="AC3">
-        <v>0.01819139241395464</v>
+        <v>0.3092564773302662</v>
       </c>
       <c r="AD3">
-        <v>7268.5</v>
+        <v>10278.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7268.5</v>
+        <v>10278.4</v>
       </c>
       <c r="AG3">
-        <v>4747.1</v>
+        <v>6637.599999999999</v>
       </c>
       <c r="AH3">
-        <v>0.5125664640424241</v>
+        <v>0.5099576292209531</v>
       </c>
       <c r="AI3">
-        <v>0.5107619442472963</v>
+        <v>0.5991105204562809</v>
       </c>
       <c r="AJ3">
-        <v>0.4071548648277755</v>
+        <v>0.401923146791324</v>
       </c>
       <c r="AK3">
-        <v>0.405412791541766</v>
+        <v>0.4911174742699015</v>
       </c>
       <c r="AL3">
-        <v>355.4</v>
+        <v>1643</v>
       </c>
       <c r="AM3">
-        <v>355.4</v>
+        <v>1643</v>
       </c>
       <c r="AN3">
-        <v>4.514035523537449</v>
+        <v>1.655830138222122</v>
       </c>
       <c r="AO3">
-        <v>4.430500844119302</v>
+        <v>3.748874010955569</v>
       </c>
       <c r="AP3">
-        <v>2.948143087815178</v>
+        <v>1.069304378644843</v>
       </c>
       <c r="AQ3">
-        <v>4.430500844119302</v>
+        <v>3.748874010955569</v>
       </c>
     </row>
   </sheetData>
